--- a/results/fad_scores_workbook.xlsx
+++ b/results/fad_scores_workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e04d2cc7e59c36d5/Documents/Python/MUSHRA/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{79B71D11-F69B-4B14-9EFE-377EBB4D0F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{899D71DE-F81F-4362-AC2F-0EAF3A8E3687}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{79B71D11-F69B-4B14-9EFE-377EBB4D0F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C0C5E9E-935E-46D0-BCD4-D2538CDCF771}"/>
   <bookViews>
     <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="10680" xr2:uid="{37C7F56F-DF35-4EA5-B3D2-2F7076C57C36}"/>
   </bookViews>
@@ -211,7 +211,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -389,6 +389,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -663,7 +669,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -674,6 +680,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1282,7 +1289,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91FBD2D8-8583-41A2-901C-50E7CF0296A1}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1290,7 +1297,7 @@
     <col min="3" max="3" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1301,7 +1308,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1312,7 +1319,7 @@
         <v>14.047346240674548</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1323,7 +1330,7 @@
         <v>4.0467930483601595</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -1334,7 +1341,7 @@
         <v>3.7225106797124141</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1344,8 +1351,9 @@
       <c r="C5" s="6">
         <v>-2.512052645897711E-7</v>
       </c>
+      <c r="F5" s="10"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>8</v>
       </c>
